--- a/data/raw/survey_responses_2.xlsx
+++ b/data/raw/survey_responses_2.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Respostas ao formulário 1" sheetId="1" r:id="rId5"/>
+    <sheet r:id="rId1" sheetId="1" name="Respostas ao formulário 1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="305">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -21,17 +24,15 @@
     </r>
     <r>
       <rPr>
-        <color rgb="FF1155CC"/>
         <u/>
+        <sz val="11"/>
+        <color rgb="FF1155cc"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </rPr>
       <t>link</t>
     </r>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">. Please read it carefully and calmly, trying to fully understand the research proposal. You will not be penalized or harmed in any way if you do not wish to participate or if you withdraw your consent at any time.
-After having received clarification on the nature of the research, its objectives and methods, I declare that I am over 18 years of age and agree to participate through the participation form, in accordance with the provisions of the Brazilian General Data Protection Law (Law No. 13,709/2018). 
-In the event of a negative response, the form will be closed, thus guaranteeing respect for the autonomy and privacy of the participants, as established by current legislation. </t>
-    </r>
   </si>
   <si>
     <t>How old are you?</t>
@@ -108,16 +109,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">important </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>are the following data quality characteristics for machine learning-enabled systems? [Precision]</t>
     </r>
@@ -128,16 +133,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">important </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>are the following data quality characteristics for machine learning-enabled systems? [Completeness]</t>
     </r>
@@ -148,16 +157,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">important </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>are the following data quality characteristics for machine learning-enabled systems? [Consistency]</t>
     </r>
@@ -168,16 +181,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">important </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>are the following data quality characteristics for machine learning-enabled systems? [Credibility]</t>
     </r>
@@ -188,16 +205,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">important </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>are the following data quality characteristics for machine learning-enabled systems? [Timeliness]</t>
     </r>
@@ -208,16 +229,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">important </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>are the following data quality characteristics for machine learning-enabled systems? [Accessibility]</t>
     </r>
@@ -228,16 +253,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">important </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>are the following data quality characteristics for machine learning-enabled systems? [Compliance]</t>
     </r>
@@ -248,16 +277,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">important </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>are the following data quality characteristics for machine learning-enabled systems? [Reliability]</t>
     </r>
@@ -268,16 +301,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">important </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>are the following data quality characteristics for machine learning-enabled systems? [Efficiency]</t>
     </r>
@@ -288,16 +325,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">important </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>are the following data quality characteristics for machine learning-enabled systems? [Traceability]</t>
     </r>
@@ -308,16 +349,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">important </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>are the following data quality characteristics for machine learning-enabled systems? [Comprehensibility]</t>
     </r>
@@ -328,16 +373,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">important </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>are the following data quality characteristics for machine learning-enabled systems? [Availability]</t>
     </r>
@@ -348,16 +397,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">important </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>are the following data quality characteristics for machine learning-enabled systems? [Recoverability]</t>
     </r>
@@ -371,16 +424,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>priority</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> of each characteristic for machine learning-based system projects? [Precision]</t>
     </r>
@@ -391,16 +448,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>priority</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> of each characteristic for machine learning-based system projects? [Completeness]</t>
     </r>
@@ -411,16 +472,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>priority</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> of each characteristic for machine learning-based system projects? [Consistency]</t>
     </r>
@@ -431,16 +496,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>priority</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> of each characteristic for machine learning-based system projects? [Credibility]</t>
     </r>
@@ -451,16 +520,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>priority</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> of each characteristic for machine learning-based system projects? [Timeliness]</t>
     </r>
@@ -471,16 +544,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>priority</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> of each characteristic for machine learning-based system projects? [Accessibility]</t>
     </r>
@@ -491,16 +568,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>priority</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> of each characteristic for machine learning-based system projects? [Compliance]</t>
     </r>
@@ -511,16 +592,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>priority</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> of each characteristic for machine learning-based system projects? [Reliability]</t>
     </r>
@@ -531,16 +616,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>priority</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> of each characteristic for machine learning-based system projects? [Efficiency]</t>
     </r>
@@ -551,16 +640,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>priority</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> of each characteristic for machine learning-based system projects? [Traceability]</t>
     </r>
@@ -571,16 +664,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>priority</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> of each characteristic for machine learning-based system projects? [Comprehensibility]</t>
     </r>
@@ -591,16 +688,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>priority</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> of each characteristic for machine learning-based system projects? [Availability]</t>
     </r>
@@ -611,16 +712,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <b/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t>priority</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
-        <color theme="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> of each characteristic for machine learning-based system projects? [Recoverability]</t>
     </r>
@@ -1106,30 +1211,317 @@
   </si>
   <si>
     <t>lucaseduardocoelho@gmail.com</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>Symmetry</t>
+  </si>
+  <si>
+    <t>Sanitize</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Provenance</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>I don't know, really not familiar with this area.</t>
+  </si>
+  <si>
+    <t>Continuous monitoring throughout the model's life cycle</t>
+  </si>
+  <si>
+    <t>Analysis of performance metrics (e.g. precision, recall), Manual review of results</t>
+  </si>
+  <si>
+    <t>No experience</t>
+  </si>
+  <si>
+    <t>Trainee</t>
+  </si>
+  <si>
+    <t>important</t>
+  </si>
+  <si>
+    <t>dataleakage</t>
+  </si>
+  <si>
+    <t>training</t>
+  </si>
+  <si>
+    <t>approximation</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>you expalined acc. but in rating scale you ask for prec.
+i ranked them as important as they are needed for the reproducibility of the results, whcih is important to have cumulative knowlede.</t>
+  </si>
+  <si>
+    <t>the availibility and similar of data was more important than the efficiency, thats then a later prolem and task for implementing efficient dataloaders, but without the date next steps are obsolete</t>
+  </si>
+  <si>
+    <t>Never</t>
+  </si>
+  <si>
+    <t>Only solo projects</t>
+  </si>
+  <si>
+    <t>Inconsistency between different data sources, Incomplete or missing data</t>
+  </si>
+  <si>
+    <t>PRC</t>
+  </si>
+  <si>
+    <t>Higher education</t>
+  </si>
+  <si>
+    <t>DevOps engineer</t>
+  </si>
+  <si>
+    <t>Full (6 to 9 years)</t>
+  </si>
+  <si>
+    <t>Qualified (in target area algorithms)</t>
+  </si>
+  <si>
+    <t>Abundant ( give space for later filtering)</t>
+  </si>
+  <si>
+    <t>Formatted (to open sourced data like opendrive)</t>
+  </si>
+  <si>
+    <t>Scale (as much as for basic algorithm verification)</t>
+  </si>
+  <si>
+    <t>Cheap ( price depends on datasets)</t>
+  </si>
+  <si>
+    <t>It is a auto parking project which we aims on parking perception tasks.</t>
+  </si>
+  <si>
+    <t>Industrial engineering consider things differently</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What everyone cares is the training result, as a mature engineer it should be essential to make system work then consider other priorities </t>
+  </si>
+  <si>
+    <t>Project management tools (Jira, Trello or Asana)</t>
+  </si>
+  <si>
+    <t>Inconsistency between different data sources, Incomplete or missing data, Errors introduced during collection and processing</t>
+  </si>
+  <si>
+    <t>michaelzhao1219@outlook.com</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Reliablity</t>
+  </si>
+  <si>
+    <t>Comprehensiblity</t>
+  </si>
+  <si>
+    <t>Compliance</t>
+  </si>
+  <si>
+    <t>incorrect labels</t>
+  </si>
+  <si>
+    <t>i wrote lightweight requirements briefling touching on behaviour (including constraints), features</t>
+  </si>
+  <si>
+    <t>For me, balancing data quality characteristics fundamentally depends on the required metrics of the ML model being built and the domain of the data. 
+If precision is the utmost priority,  for instance in a high-stakes classification task , I would favor data accuracy, credibility, and timeliness over attributes like computational efficiency. 
+On the other hand, in a task like text classification where introducing false positives haves little harm, precision in the data becomes less critical, and I will instead prioritize completeness, accessibility, and traceability. 
+An example from my research is my work on design discussion detection using transformer models, where the scarcity of labeled data and high annotation costs meant I had to prioritize data completeness and accessibility — accepting a reduced but well-curated dataset — over having a perfectly precise, fully annotated corpus. So basically, the ML model's target metrics and the risk profile of its errors should always drive which data quality characteristics you optimize for.</t>
+  </si>
+  <si>
+    <t>Initial assessment during data collection and preparation, There is no formal strategy for ensuring data quality during development.</t>
+  </si>
+  <si>
+    <t>Structured language (text)</t>
+  </si>
+  <si>
+    <t>Inconsistency between different data sources, Lack of standardization in data formats, Outdated or unreliable data</t>
+  </si>
+  <si>
+    <t>Business</t>
+  </si>
+  <si>
+    <t>Visualisation</t>
+  </si>
+  <si>
+    <t>Cleaning</t>
+  </si>
+  <si>
+    <t>EDA</t>
+  </si>
+  <si>
+    <t>Outlier</t>
+  </si>
+  <si>
+    <t>Customer Churn Modeling in Card products. Talking to the business stakeholders to understand the definition of the churn for the business</t>
+  </si>
+  <si>
+    <t>It really depends on the business requirements and the problem that we are solving</t>
+  </si>
+  <si>
+    <t>Centralized documentation (systems such as Confluence, Google Docs or Notion), Alignment meetings, Periodic reports</t>
+  </si>
+  <si>
+    <t>Variance</t>
+  </si>
+  <si>
+    <t>In Finance, the focus was often on speed and precision. In Healthcare, the focus is more on explainability and safety.</t>
+  </si>
+  <si>
+    <t>Continuous monitoring throughout the model's life cycle, Test sets are applied to validate the consistency, completeness and accuracy of the data before it is used for training.</t>
+  </si>
+  <si>
+    <t>Project management tools (Jira, Trello or Asana), Alignment meetings</t>
+  </si>
+  <si>
+    <t>Inconsistency between different data sources, Incomplete or missing data, Lack of standardization in data formats, Errors introduced during collection and processing</t>
+  </si>
+  <si>
+    <t>United States, North Carolina</t>
+  </si>
+  <si>
+    <t>Tech manager</t>
+  </si>
+  <si>
+    <t>Consistency</t>
+  </si>
+  <si>
+    <t>Representativeness</t>
+  </si>
+  <si>
+    <t>Standardization</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>As a tech lead, I have been directly involved in defining, analyzing, and documenting requirements. This process usually involves coordinating with stakeholders (POs, CPO, etc) to understand business needs, define expectations, and translate those requirements into technical specifications and tasks.</t>
+  </si>
+  <si>
+    <t>I balance them according to the desired goals and the systems constraints. For example, in IoT or real-time systems, I would prioritize efficiency. In contrast, in critical systems, I would prioritize accuracy and reliability. The decision depends on how the model will be used in practice.</t>
+  </si>
+  <si>
+    <t>Alignment meetings, Periodic reports</t>
+  </si>
+  <si>
+    <t>Brasil, Rio de Janeiro</t>
+  </si>
+  <si>
+    <t>Limpeza</t>
+  </si>
+  <si>
+    <t>Padronização</t>
+  </si>
+  <si>
+    <t>Normalização</t>
+  </si>
+  <si>
+    <t>Validação</t>
+  </si>
+  <si>
+    <t>Consistência</t>
+  </si>
+  <si>
+    <t>Minha atuação na área de ER sempre esteve restrita a pressupostos metodológicos, atuando mais como um usuário de documentação de requisitos do que alguém atuante na definição dos mesmos (com exceção dos casos pontuais nos quais foi necessária uma intervenção da minha parte para corrigir um equívoco da documentação ou concluir pela inexequibilidade do requisito para um projeto).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Em específico para essas características definidas no enunciado, é fácil equilibrá-las, já que não existe competitividade entre elas. Contudo, entendo que, uma vez que a precisão dos dados tenha sido alcançada e que a compreensão a respeito deles tenha sido garantida (seja pela clareza da documentação, compreensão da equipe de desenvolvimento ou pela presença de um "especialista de domínio"), o ponto crítico é a eficiência, que deve ser garantida tanto pelo tratamento dos dados quanto pela infraestrutura utilizada para o processamento: 1) é preciso que os dados sejam otimizados para o processamento (recentemente, consegui tonar um projeto exequível passando os dados do formato separado por vírgulas -- csv -- para o formato apache parquet, geralmente utilizado em projetos de Big Data e, assim, o tornei mais eficiente, passando-o de 8gb para 800mb); 2) contudo, para tudo há um limite e, por vezes, é necessário decidir se não seria estratégico realizar um upgrade vertical ou horizontal da infraestrutura física utilizada, opções essas dentre as quais o último caso (scale-out) costuma apresentar resultados melhores, por se tratar de um processamento distribuído. </t>
+  </si>
+  <si>
+    <t>Structured language (text), Project management tools (Jira, Trello or Asana), Alignment meetings, Periodic reports</t>
+  </si>
+  <si>
+    <t>Incomplete or missing data, Outdated or unreliable data, Errors introduced during collection and processing, Difficulty in data traceability and versioning</t>
+  </si>
+  <si>
+    <t>danieldelunamarques@gmail.com</t>
+  </si>
+  <si>
+    <t>Brazil, Rio de Janeiro</t>
+  </si>
+  <si>
+    <t>High school</t>
+  </si>
+  <si>
+    <t>Nullity</t>
+  </si>
+  <si>
+    <t>Multicollinearity</t>
+  </si>
+  <si>
+    <t>Distinction</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>I've only made very small personal projects so i basically did little to no requirements engineering.</t>
+  </si>
+  <si>
+    <t>In one of my latest machine learning projects using an adult income dataset, I chose a logistic regression model, a decision that prioritized an interpretable and reproducible architecture over more complex models. Furthermore, to reconcile computational efficiency with predictive power, I created a new atribute (capital-net) by consolidanting both capital gain and loss, simplifying the input matrix while retaining essential data.</t>
+  </si>
+  <si>
+    <t>Incomplete or missing data, Lack of standardization in data formats, Outdated or unreliable data</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>Foundation</t>
+  </si>
+  <si>
+    <t>I do this very little and in a more incremental way. At work, we usually get ahead of client requests, so we bring prototypes to gather feedback. From there, we keep improving the project and adapting the requirements in practice.</t>
+  </si>
+  <si>
+    <t>Balancing data quality in real-world machine learning projects is essentially a constant game of trade-offs, as you can rarely optimize for everything at once. For instance, highly accurate models demand massive amounts of computing power, so you often have to settle for a slightly less precise but much faster model just to make it practical to run in production. Similarly, while neatly organized and highly structured databases are great for developers to read and understand, they are notoriously slow for training, meaning we usually end up flattening the data into ugly, denormalized tables so the algorithms can ingest them efficiently. Even when building the dataset itself, trying to keep every single messy record just to maximize completeness usually introduces too much noise, making it far better to simply throw out the bad data and accept a smaller dataset in exchange for a much more accurate and reliable model.</t>
+  </si>
+  <si>
+    <t>Inconsistency between different data sources, Outdated or unreliable data</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FF0000ff"/>
       <name val="Roboto"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1137,114 +1529,74 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="10">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Respostas ao formulário 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
-    </tableStyle>
-  </tableStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:BJ10" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:BJ20" displayName="Form_Responses" name="Form_Responses" id="1" totalsRowShown="0">
+  <autoFilter ref="A1:BJ20"/>
   <tableColumns count="62">
     <tableColumn name="Carimbo de data/hora" id="1"/>
     <tableColumn name="This informed consent form aims to ensure your rights as a participant and is available at this link. Please read it carefully and calmly, trying to fully understand the research proposal. You will not be penalized or harmed in any way if you do not wish to participate or if you withdraw your consent at any time._x000a__x000a_After having received clarification on the nature of the research, its objectives and methods, I declare that I am over 18 years of age and agree to participate through the participation form, in accordance with the provisions of the Brazilian General Data Protection Law (Law No. 13,709/2018). _x000a__x000a_In the event of a negative response, the form will be closed, thus guaranteeing respect for the autonomy and privacy of the participants, as established by current legislation. " id="2"/>
@@ -1309,19 +1661,19 @@
     <tableColumn name="How often do you receive support from other teams (e.g. data team, data scientists) to deal with data quality issues?  " id="61"/>
     <tableColumn name="If you would like to receive the results of this study and take part in a future interview on Data Quality, please enter your e-mail address." id="62"/>
   </tableColumns>
-  <tableStyleInfo name="Respostas ao formulário 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="1" showFirstColumn="1"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -1348,22 +1700,82 @@
         <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1375,2008 +1787,3913 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot rev="0" lon="0" lat="0"/>
+            </a:camera>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:BJ20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21.25"/>
-    <col customWidth="1" min="2" max="2" width="37.63"/>
-    <col customWidth="1" min="3" max="3" width="18.88"/>
-    <col customWidth="1" min="4" max="4" width="37.63"/>
-    <col customWidth="1" min="5" max="5" width="20.0"/>
-    <col customWidth="1" min="6" max="6" width="28.25"/>
-    <col customWidth="1" min="7" max="7" width="37.63"/>
-    <col customWidth="1" min="8" max="8" width="31.13"/>
-    <col customWidth="1" min="9" max="19" width="37.63"/>
-    <col customWidth="1" min="20" max="24" width="18.88"/>
-    <col customWidth="1" min="25" max="62" width="37.63"/>
-    <col customWidth="1" min="63" max="68" width="18.88"/>
+    <col min="1" max="1" style="7" width="21.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="18.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="20.005" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="28.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="31.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="9" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="8" width="18.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="8" width="18.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="8" width="18.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="8" width="18.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="8" width="18.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="32" max="32" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="33" max="33" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="34" max="34" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="35" max="35" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="36" max="36" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="37" max="37" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="38" max="38" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="39" max="39" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="40" max="40" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="41" max="41" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="42" max="42" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="43" max="43" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="44" max="44" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="45" max="45" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="46" max="46" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="47" max="47" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="48" max="48" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="49" max="49" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="50" max="50" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="51" max="51" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="52" max="52" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="53" max="53" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="54" max="54" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="55" max="55" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="56" max="56" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="57" max="57" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="58" max="58" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="59" max="59" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="60" max="60" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="61" max="61" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="62" max="62" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BB1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BF1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BJ1" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="3">
-        <v>45709.26169591435</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1">
+        <v>45709.26170138889</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="I2" s="5">
+        <v>4</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="O2" s="4" t="s">
+      <c r="N2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="R2" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="T2" s="4" t="s">
+      <c r="R2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="U2" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="V2" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="W2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="X2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="Y2" s="4" t="s">
+      <c r="Y2" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Z2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC2" s="4" t="s">
+      <c r="Z2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AD2" s="4" t="s">
+      <c r="AD2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AE2" s="4" t="s">
+      <c r="AE2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="AF2" s="4" t="s">
+      <c r="AF2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AG2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL2" s="4" t="s">
+      <c r="AG2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="AM2" s="4" t="s">
+      <c r="AM2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="AN2" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AO2" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AP2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AQ2" s="4" t="s">
+      <c r="AN2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AP2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AQ2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="AR2" s="4" t="s">
+      <c r="AR2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="AS2" s="4" t="s">
+      <c r="AS2" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="AT2" s="4" t="s">
+      <c r="AT2" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="AU2" s="4" t="s">
+      <c r="AU2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="AV2" s="4" t="s">
+      <c r="AV2" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="AW2" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX2" s="4" t="s">
+      <c r="AW2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="AY2" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AZ2" s="4" t="s">
+      <c r="AY2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="BA2" s="5"/>
-      <c r="BB2" s="4" t="s">
+      <c r="BA2" s="3"/>
+      <c r="BB2" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="BC2" s="4" t="s">
+      <c r="BC2" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="BD2" s="4" t="s">
+      <c r="BD2" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="BE2" s="4" t="s">
+      <c r="BE2" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="BF2" s="4" t="s">
+      <c r="BF2" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="BG2" s="4" t="s">
+      <c r="BG2" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="BH2" s="4" t="s">
+      <c r="BH2" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="BI2" s="4" t="s">
+      <c r="BI2" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="BJ2" s="5"/>
+      <c r="BJ2" s="3"/>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="3">
-        <v>45709.51199293981</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1">
+        <v>45709.51199074074</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I3" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L3" s="4" t="s">
+      <c r="I3" s="5">
+        <v>4</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="P3" s="4" t="s">
+      <c r="M3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="Q3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="T3" s="4" t="s">
+      <c r="Q3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="U3" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="V3" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="W3" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="X3" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Y3" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="Z3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL3" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM3" s="4" t="s">
+      <c r="Z3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM3" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="AN3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AP3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AR3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AT3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AU3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AV3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AW3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AX3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AZ3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="BA3" s="5"/>
-      <c r="BB3" s="4" t="s">
+      <c r="AN3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="BA3" s="3"/>
+      <c r="BB3" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="BC3" s="4" t="s">
+      <c r="BC3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="BD3" s="4" t="s">
+      <c r="BD3" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="BE3" s="4" t="s">
+      <c r="BE3" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="BF3" s="4" t="s">
+      <c r="BF3" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="BG3" s="4" t="s">
+      <c r="BG3" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="BH3" s="4" t="s">
+      <c r="BH3" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="BI3" s="4" t="s">
+      <c r="BI3" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="BJ3" s="5"/>
+      <c r="BJ3" s="3"/>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="3">
-        <v>45713.42661681713</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="30.75">
+      <c r="A4" s="1">
+        <v>45713.426620370374</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I4" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" s="4" t="s">
+      <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="O4" s="4" t="s">
+      <c r="M4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="P4" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q4" s="4" t="s">
+      <c r="P4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q4" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="S4" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="T4" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="U4" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="V4" s="4" t="s">
+      <c r="V4" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="W4" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="X4" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Y4" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="Z4" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA4" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE4" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH4" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI4" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ4" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK4" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL4" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM4" s="5"/>
-      <c r="AN4" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AO4" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AQ4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AR4" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS4" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AT4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AU4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AV4" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW4" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AX4" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY4" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AZ4" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="BA4" s="5"/>
-      <c r="BB4" s="4" t="s">
+      <c r="Z4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM4" s="3"/>
+      <c r="AN4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AU4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="BA4" s="3"/>
+      <c r="BB4" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="BC4" s="4" t="s">
+      <c r="BC4" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="BD4" s="4" t="s">
+      <c r="BD4" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="BE4" s="4" t="s">
+      <c r="BE4" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="BF4" s="4" t="s">
+      <c r="BF4" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="BG4" s="4" t="s">
+      <c r="BG4" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="BH4" s="4" t="s">
+      <c r="BH4" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="BI4" s="4" t="s">
+      <c r="BI4" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="BJ4" s="4" t="s">
+      <c r="BJ4" s="3" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="3">
-        <v>45714.385825219906</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1">
+        <v>45714.38582175926</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I5" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="J5" s="4" t="s">
+      <c r="I5" s="5">
+        <v>6</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="R5" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="S5" s="4" t="s">
+      <c r="R5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="T5" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="U5" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="V5" s="4" t="s">
+      <c r="V5" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="W5" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="Y5" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="Z5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA5" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AG5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH5" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI5" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL5" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM5" s="5"/>
-      <c r="AN5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AO5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AQ5" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AR5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AT5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AU5" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AV5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AX5" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY5" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AZ5" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="BA5" s="5"/>
-      <c r="BB5" s="4" t="s">
+      <c r="Z5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM5" s="3"/>
+      <c r="AN5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AQ5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AU5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX5" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AZ5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA5" s="3"/>
+      <c r="BB5" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="BC5" s="4" t="s">
+      <c r="BC5" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="BD5" s="4" t="s">
+      <c r="BD5" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="BE5" s="4" t="s">
+      <c r="BE5" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="BF5" s="4" t="s">
+      <c r="BF5" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="BG5" s="4" t="s">
+      <c r="BG5" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="BH5" s="4" t="s">
+      <c r="BH5" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="BI5" s="4" t="s">
+      <c r="BI5" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="BJ5" s="4" t="s">
+      <c r="BJ5" s="3" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="3">
-        <v>45714.43988090278</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1">
+        <v>45714.439884259256</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>68</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K6" s="4" t="s">
+      <c r="J6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="P6" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="Q6" s="4" t="s">
+      <c r="Q6" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="R6" s="4" t="s">
+      <c r="R6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="S6" s="4" t="s">
+      <c r="S6" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="T6" s="4" t="s">
+      <c r="T6" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="U6" s="4" t="s">
+      <c r="U6" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="V6" s="4" t="s">
+      <c r="V6" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="W6" s="4" t="s">
+      <c r="W6" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="X6" s="4" t="s">
+      <c r="X6" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="Y6" s="4" t="s">
+      <c r="Y6" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="Z6" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA6" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC6" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK6" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM6" s="4" t="s">
+      <c r="Z6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM6" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="AN6" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO6" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AP6" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AQ6" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AR6" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AT6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AU6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV6" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AY6" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AZ6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="BA6" s="5"/>
-      <c r="BB6" s="4" t="s">
+      <c r="AN6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AP6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AQ6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA6" s="3"/>
+      <c r="BB6" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="BC6" s="4" t="s">
+      <c r="BC6" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="BD6" s="4" t="s">
+      <c r="BD6" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="BE6" s="4" t="s">
+      <c r="BE6" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="BF6" s="4" t="s">
+      <c r="BF6" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="BG6" s="4" t="s">
+      <c r="BG6" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="BH6" s="4" t="s">
+      <c r="BH6" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="BI6" s="4" t="s">
+      <c r="BI6" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="BJ6" s="4" t="s">
+      <c r="BJ6" s="3" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="3">
-        <v>45716.4519089699</v>
-      </c>
-      <c r="B7" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1">
+        <v>45716.45190972222</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I7" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q7" s="4" t="s">
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="R7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="T7" s="4" t="s">
+      <c r="R7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T7" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="U7" s="4" t="s">
+      <c r="U7" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="V7" s="4" t="s">
+      <c r="V7" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="W7" s="4" t="s">
+      <c r="W7" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="X7" s="4" t="s">
+      <c r="X7" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="Y7" s="4" t="s">
+      <c r="Y7" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="Z7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AH7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AI7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AM7" s="5"/>
-      <c r="AN7" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO7" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP7" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AQ7" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AR7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AS7" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AT7" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AU7" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AV7" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AW7" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AX7" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY7" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AZ7" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="BA7" s="5"/>
-      <c r="BB7" s="4" t="s">
+      <c r="Z7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM7" s="3"/>
+      <c r="AN7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AQ7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS7" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AU7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AZ7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="BA7" s="3"/>
+      <c r="BB7" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="BC7" s="4" t="s">
+      <c r="BC7" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="BD7" s="4" t="s">
+      <c r="BD7" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="BE7" s="4" t="s">
+      <c r="BE7" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="BF7" s="4" t="s">
+      <c r="BF7" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="BG7" s="4" t="s">
+      <c r="BG7" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="BH7" s="4" t="s">
+      <c r="BH7" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="BI7" s="4" t="s">
+      <c r="BI7" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="BJ7" s="5"/>
+      <c r="BJ7" s="3"/>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="3">
-        <v>45720.35128591435</v>
-      </c>
-      <c r="B8" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1">
+        <v>45720.35128472222</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J8" s="4" t="s">
+      <c r="I8" s="5">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="P8" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="Q8" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="R8" s="4" t="s">
+      <c r="R8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="S8" s="4" t="s">
+      <c r="S8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="T8" s="4" t="s">
+      <c r="T8" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="U8" s="4" t="s">
+      <c r="U8" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="V8" s="4" t="s">
+      <c r="V8" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="W8" s="4" t="s">
+      <c r="W8" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="X8" s="4" t="s">
+      <c r="X8" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="Y8" s="4" t="s">
+      <c r="Y8" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="Z8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA8" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD8" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AE8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ8" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK8" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM8" s="5"/>
-      <c r="AN8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO8" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AP8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AQ8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR8" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AS8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AT8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AU8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AV8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AX8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY8" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AZ8" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="BA8" s="5"/>
-      <c r="BB8" s="4" t="s">
+      <c r="Z8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM8" s="3"/>
+      <c r="AN8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AP8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AQ8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AU8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AZ8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="BA8" s="3"/>
+      <c r="BB8" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="BC8" s="4" t="s">
+      <c r="BC8" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="BD8" s="4" t="s">
+      <c r="BD8" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="BE8" s="4" t="s">
+      <c r="BE8" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="BF8" s="4" t="s">
+      <c r="BF8" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="BG8" s="4" t="s">
+      <c r="BG8" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="BH8" s="4" t="s">
+      <c r="BH8" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="BI8" s="4" t="s">
+      <c r="BI8" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="BJ8" s="5"/>
+      <c r="BJ8" s="3"/>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="3">
-        <v>45723.271467094906</v>
-      </c>
-      <c r="B9" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1">
+        <v>45723.271469907406</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I9" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="J9" s="4" t="s">
+      <c r="I9" s="5">
+        <v>4</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="N9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="O9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="P9" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="Q9" s="4" t="s">
+      <c r="Q9" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="R9" s="4" t="s">
+      <c r="R9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="S9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="T9" s="4" t="s">
+      <c r="S9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T9" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="U9" s="4" t="s">
+      <c r="U9" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="V9" s="4" t="s">
+      <c r="V9" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="W9" s="4" t="s">
+      <c r="W9" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="X9" s="4" t="s">
+      <c r="X9" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="Y9" s="4" t="s">
+      <c r="Y9" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="Z9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK9" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM9" s="5"/>
-      <c r="AN9" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AO9" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AP9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AQ9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AR9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AS9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AT9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AU9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV9" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AW9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX9" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY9" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AZ9" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="BA9" s="5"/>
-      <c r="BB9" s="4" t="s">
+      <c r="Z9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM9" s="3"/>
+      <c r="AN9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AQ9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA9" s="3"/>
+      <c r="BB9" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="BC9" s="4" t="s">
+      <c r="BC9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="BD9" s="4" t="s">
+      <c r="BD9" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="BE9" s="4" t="s">
+      <c r="BE9" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="BF9" s="4" t="s">
+      <c r="BF9" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="BG9" s="4" t="s">
+      <c r="BG9" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="BH9" s="4" t="s">
+      <c r="BH9" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="BI9" s="4" t="s">
+      <c r="BI9" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="BJ9" s="4" t="s">
+      <c r="BJ9" s="3" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="3">
-        <v>45726.274782569446</v>
-      </c>
-      <c r="B10" s="4" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1">
+        <v>45726.27478009259</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I10" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L10" s="4" t="s">
+      <c r="I10" s="5">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="O10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="P10" s="4" t="s">
+      <c r="P10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="Q10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="R10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="S10" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="T10" s="4" t="s">
+      <c r="S10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T10" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="U10" s="4" t="s">
+      <c r="U10" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="V10" s="4" t="s">
+      <c r="V10" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="W10" s="4" t="s">
+      <c r="W10" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="X10" s="4" t="s">
+      <c r="X10" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="Y10" s="4" t="s">
+      <c r="Y10" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="Z10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC10" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE10" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AJ10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="AK10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM10" s="5"/>
-      <c r="AN10" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="AO10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AP10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AQ10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AR10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AS10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AT10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AU10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AV10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AW10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="AX10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="AY10" s="4" t="s">
+      <c r="Z10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM10" s="3"/>
+      <c r="AN10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AQ10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="AZ10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="BA10" s="5"/>
-      <c r="BB10" s="4" t="s">
+      <c r="AZ10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA10" s="3"/>
+      <c r="BB10" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="BC10" s="4" t="s">
+      <c r="BC10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="BD10" s="4" t="s">
+      <c r="BD10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="BE10" s="4" t="s">
+      <c r="BE10" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="BF10" s="4" t="s">
+      <c r="BF10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="BG10" s="4" t="s">
+      <c r="BG10" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="BH10" s="4" t="s">
+      <c r="BH10" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="BI10" s="4" t="s">
+      <c r="BI10" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="BJ10" s="4" t="s">
+      <c r="BJ10" s="3" t="s">
         <v>211</v>
       </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1">
+        <v>46139.95429398148</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="5">
+        <v>2</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="Y11" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM11" s="6"/>
+      <c r="AN11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AQ11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY11" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA11" s="6"/>
+      <c r="BB11" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="BC11" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BD11" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="BE11" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BG11" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="BH11" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="BI11" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BJ11" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="30.75">
+      <c r="A12" s="1">
+        <v>46140.44697916666</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I12" s="5">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM12" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="AN12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AU12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AW12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AZ12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="BA12" s="6"/>
+      <c r="BB12" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="BC12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BD12" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="BE12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="BF12" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="BG12" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="BH12" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="BI12" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="BJ12" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1">
+        <v>46140.88291666667</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I13" s="5">
+        <v>15</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="W13" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="X13" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="Y13" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM13" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="AN13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AP13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AQ13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AR13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AS13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AV13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AZ13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="BA13" s="6"/>
+      <c r="BB13" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="BC13" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="BD13" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE13" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BF13" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="BG13" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="BH13" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="BI13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="BJ13" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="81.75">
+      <c r="A14" s="1">
+        <v>46141.38967592592</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" s="5">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM14" s="6"/>
+      <c r="AN14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AP14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AQ14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AS14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AV14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AW14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AX14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AZ14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA14" s="6"/>
+      <c r="BB14" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="BC14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BD14" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="BE14" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF14" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BG14" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="BH14" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="BI14" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="BJ14" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="1">
+        <v>46141.91211805555</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I15" s="5">
+        <v>7</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM15" s="6"/>
+      <c r="AN15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AP15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AQ15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AT15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AU15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AW15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA15" s="6"/>
+      <c r="BB15" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="BC15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BD15" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="BE15" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BG15" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="BH15" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="BI15" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BJ15" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="1">
+        <v>46141.91679398148</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I16" s="5">
+        <v>2</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="X16" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y16" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AE16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM16" s="6"/>
+      <c r="AN16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AP16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AQ16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AU16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AZ16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="BA16" s="6"/>
+      <c r="BB16" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="BC16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BD16" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="BE16" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BF16" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="BG16" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="BH16" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="BI16" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="BJ16" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="1">
+        <v>46141.96266203704</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I17" s="5">
+        <v>6</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI17" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM17" s="6"/>
+      <c r="AN17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AU17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="BA17" s="6"/>
+      <c r="BB17" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="BC17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BD17" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE17" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="BF17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="BG17" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="BH17" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="BI17" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BJ17" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="1">
+        <v>46142.355844907404</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I18" s="5">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF18" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM18" s="6"/>
+      <c r="AN18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AP18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AS18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AT18" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="AU18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW18" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AY18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AZ18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="BA18" s="6"/>
+      <c r="BB18" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="BC18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BD18" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE18" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="BF18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="BG18" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="BH18" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="BI18" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="BJ18" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="1">
+        <v>46142.36699074074</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I19" s="5">
+        <v>2</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="W19" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="X19" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y19" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="Z19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM19" s="6"/>
+      <c r="AN19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AP19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AR19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AT19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AV19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AX19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AY19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AZ19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BA19" s="6"/>
+      <c r="BB19" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="BC19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BD19" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="BE19" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="BF19" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BG19" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="BH19" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="BI19" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="BJ19" s="6"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="1">
+        <v>46142.39351851852</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I20" s="5">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AL20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM20" s="6"/>
+      <c r="AN20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AR20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AS20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AU20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW20" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AY20" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AZ20" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="BA20" s="6"/>
+      <c r="BB20" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="BC20" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="BD20" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="BE20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="BF20" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="BG20" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="BH20" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="BI20" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BJ20" s="6"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="B1"/>
-  </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/raw/survey_responses_2.xlsx
+++ b/data/raw/survey_responses_2.xlsx
@@ -1551,7 +1551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1572,13 +1572,16 @@
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1994,7 +1997,7 @@
     <col min="36" max="36" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
     <col min="37" max="37" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
     <col min="38" max="38" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="39" max="39" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="39" max="39" style="10" width="37.57642857142857" customWidth="1" bestFit="1"/>
     <col min="40" max="40" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
     <col min="41" max="41" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
     <col min="42" max="42" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
@@ -2008,7 +2011,7 @@
     <col min="50" max="50" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
     <col min="51" max="51" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
     <col min="52" max="52" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="53" max="53" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="53" max="53" style="10" width="37.57642857142857" customWidth="1" bestFit="1"/>
     <col min="54" max="54" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
     <col min="55" max="55" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
     <col min="56" max="56" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
@@ -2017,7 +2020,7 @@
     <col min="59" max="59" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
     <col min="60" max="60" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
     <col min="61" max="61" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="62" max="62" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="62" max="62" style="10" width="37.57642857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5">
@@ -2576,7 +2579,7 @@
       </c>
       <c r="BJ3" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="30.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="32.25">
       <c r="A4" s="1">
         <v>45713.426620370374</v>
       </c>
@@ -4044,7 +4047,7 @@
       </c>
       <c r="BJ11" s="6"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="30.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="32.25">
       <c r="A12" s="1">
         <v>46140.44697916666</v>
       </c>
@@ -4414,7 +4417,7 @@
         <v>247</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="81.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="84.75">
       <c r="A14" s="1">
         <v>46141.38967592592</v>
       </c>

--- a/data/raw/survey_responses_2.xlsx
+++ b/data/raw/survey_responses_2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="304">
   <si>
     <t>Carimbo de data/hora</t>
   </si>
@@ -1025,9 +1025,6 @@
   </si>
   <si>
     <t>Software Developer (Backend, front-end, fullstack)</t>
-  </si>
-  <si>
-    <t>7-10, mostly university projects</t>
   </si>
   <si>
     <t>Very low</t>
@@ -2972,8 +2969,8 @@
       <c r="H6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>150</v>
+      <c r="I6" s="4">
+        <v>8</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>70</v>
@@ -2997,7 +2994,7 @@
         <v>136</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R6" s="3" t="s">
         <v>71</v>
@@ -3006,64 +3003,64 @@
         <v>69</v>
       </c>
       <c r="T6" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="U6" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="U6" s="3" t="s">
+      <c r="V6" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="V6" s="3" t="s">
+      <c r="W6" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="W6" s="3" t="s">
+      <c r="X6" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="X6" s="3" t="s">
+      <c r="Y6" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="Y6" s="3" t="s">
+      <c r="Z6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC6" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AJ6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AL6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM6" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="Z6" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA6" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AB6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AC6" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AE6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AF6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AG6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI6" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ6" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL6" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM6" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="AN6" s="3" t="s">
         <v>85</v>
@@ -3106,7 +3103,7 @@
       </c>
       <c r="BA6" s="3"/>
       <c r="BB6" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BC6" s="3" t="s">
         <v>89</v>
@@ -3118,19 +3115,19 @@
         <v>110</v>
       </c>
       <c r="BF6" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="BG6" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="BG6" s="3" t="s">
+      <c r="BH6" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="BH6" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="BI6" s="3" t="s">
         <v>95</v>
       </c>
       <c r="BJ6" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -3141,10 +3138,10 @@
         <v>62</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>65</v>
@@ -3192,22 +3189,22 @@
         <v>70</v>
       </c>
       <c r="T7" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="U7" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="U7" s="3" t="s">
+      <c r="V7" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="V7" s="3" t="s">
+      <c r="W7" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="W7" s="3" t="s">
+      <c r="X7" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="X7" s="3" t="s">
+      <c r="Y7" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="Y7" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="Z7" s="3" t="s">
         <v>79</v>
@@ -3290,25 +3287,25 @@
       </c>
       <c r="BA7" s="3"/>
       <c r="BB7" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="BC7" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="BC7" s="3" t="s">
+      <c r="BD7" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="BD7" s="3" t="s">
+      <c r="BE7" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="BE7" s="3" t="s">
-        <v>175</v>
-      </c>
       <c r="BF7" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="BG7" s="3" t="s">
         <v>93</v>
       </c>
       <c r="BH7" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BI7" s="3" t="s">
         <v>131</v>
@@ -3335,7 +3332,7 @@
         <v>66</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>68</v>
@@ -3362,10 +3359,10 @@
         <v>71</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>69</v>
@@ -3374,22 +3371,22 @@
         <v>69</v>
       </c>
       <c r="T8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="U8" s="3" t="s">
+      <c r="V8" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="V8" s="3" t="s">
+      <c r="W8" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="W8" s="3" t="s">
+      <c r="X8" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="X8" s="3" t="s">
+      <c r="Y8" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>183</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>80</v>
@@ -3472,25 +3469,25 @@
       </c>
       <c r="BA8" s="3"/>
       <c r="BB8" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="BC8" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="BC8" s="3" t="s">
-        <v>185</v>
       </c>
       <c r="BD8" s="3" t="s">
         <v>143</v>
       </c>
       <c r="BE8" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BF8" s="3" t="s">
         <v>92</v>
       </c>
       <c r="BG8" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="BH8" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="BH8" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="BI8" s="3" t="s">
         <v>131</v>
@@ -3508,7 +3505,7 @@
         <v>115</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>65</v>
@@ -3556,22 +3553,22 @@
         <v>70</v>
       </c>
       <c r="T9" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="U9" s="3" t="s">
+      <c r="V9" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="V9" s="3" t="s">
+      <c r="W9" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="W9" s="3" t="s">
+      <c r="X9" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="X9" s="3" t="s">
+      <c r="Y9" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>80</v>
@@ -3654,13 +3651,13 @@
       </c>
       <c r="BA9" s="3"/>
       <c r="BB9" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BC9" s="3" t="s">
         <v>89</v>
       </c>
       <c r="BD9" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BE9" s="3" t="s">
         <v>127</v>
@@ -3672,13 +3669,13 @@
         <v>93</v>
       </c>
       <c r="BH9" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BI9" s="3" t="s">
         <v>95</v>
       </c>
       <c r="BJ9" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -3692,7 +3689,7 @@
         <v>115</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>65</v>
@@ -3722,7 +3719,7 @@
         <v>136</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>69</v>
@@ -3740,22 +3737,22 @@
         <v>70</v>
       </c>
       <c r="T10" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="U10" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="U10" s="3" t="s">
+      <c r="V10" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="V10" s="3" t="s">
+      <c r="W10" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="W10" s="3" t="s">
+      <c r="X10" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="X10" s="3" t="s">
+      <c r="Y10" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="Y10" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="Z10" s="3" t="s">
         <v>80</v>
@@ -3838,7 +3835,7 @@
       </c>
       <c r="BA10" s="3"/>
       <c r="BB10" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="BC10" s="3" t="s">
         <v>89</v>
@@ -3847,22 +3844,22 @@
         <v>90</v>
       </c>
       <c r="BE10" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="BF10" s="3" t="s">
         <v>92</v>
       </c>
       <c r="BG10" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="BH10" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="BI10" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="BI10" s="3" t="s">
+      <c r="BJ10" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="BJ10" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
@@ -3876,7 +3873,7 @@
         <v>115</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>65</v>
@@ -3906,7 +3903,7 @@
         <v>136</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>71</v>
@@ -3927,19 +3924,19 @@
         <v>137</v>
       </c>
       <c r="U11" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="V11" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="V11" s="3" t="s">
+      <c r="W11" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="W11" s="3" t="s">
+      <c r="X11" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="X11" s="3" t="s">
+      <c r="Y11" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="Y11" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="Z11" s="3" t="s">
         <v>80</v>
@@ -4022,28 +4019,28 @@
       </c>
       <c r="BA11" s="6"/>
       <c r="BB11" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="BC11" s="3" t="s">
         <v>89</v>
       </c>
       <c r="BD11" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="BE11" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="BE11" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="BF11" s="3" t="s">
         <v>128</v>
       </c>
       <c r="BG11" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BH11" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BI11" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BJ11" s="6"/>
     </row>
@@ -4070,7 +4067,7 @@
         <v>149</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I12" s="5">
         <v>3</v>
@@ -4094,10 +4091,10 @@
         <v>71</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>71</v>
@@ -4106,22 +4103,22 @@
         <v>70</v>
       </c>
       <c r="T12" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="V12" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="V12" s="3" t="s">
+      <c r="W12" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="W12" s="3" t="s">
+      <c r="X12" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="X12" s="3" t="s">
+      <c r="Y12" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="Y12" s="3" t="s">
-        <v>227</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>80</v>
@@ -4163,7 +4160,7 @@
         <v>78</v>
       </c>
       <c r="AM12" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AN12" s="3" t="s">
         <v>78</v>
@@ -4206,7 +4203,7 @@
       </c>
       <c r="BA12" s="6"/>
       <c r="BB12" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="BC12" s="3" t="s">
         <v>89</v>
@@ -4218,16 +4215,16 @@
         <v>91</v>
       </c>
       <c r="BF12" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="BG12" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="BG12" s="3" t="s">
+      <c r="BH12" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="BH12" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="BI12" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BJ12" s="6"/>
     </row>
@@ -4242,19 +4239,19 @@
         <v>115</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>65</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="I13" s="5">
         <v>15</v>
@@ -4290,22 +4287,22 @@
         <v>70</v>
       </c>
       <c r="T13" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="U13" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="U13" s="3" t="s">
+      <c r="V13" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="V13" s="3" t="s">
+      <c r="W13" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="W13" s="3" t="s">
+      <c r="X13" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="X13" s="3" t="s">
+      <c r="Y13" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="Y13" s="3" t="s">
-        <v>242</v>
       </c>
       <c r="Z13" s="3" t="s">
         <v>79</v>
@@ -4347,7 +4344,7 @@
         <v>78</v>
       </c>
       <c r="AM13" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AN13" s="3" t="s">
         <v>85</v>
@@ -4390,10 +4387,10 @@
       </c>
       <c r="BA13" s="6"/>
       <c r="BB13" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="BC13" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BD13" s="3" t="s">
         <v>109</v>
@@ -4405,16 +4402,16 @@
         <v>111</v>
       </c>
       <c r="BG13" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="BH13" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="BH13" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="BI13" s="3" t="s">
         <v>131</v>
       </c>
       <c r="BJ13" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="84.75">
@@ -4428,7 +4425,7 @@
         <v>115</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>65</v>
@@ -4476,22 +4473,22 @@
         <v>70</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="W14" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="X14" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>252</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>253</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>79</v>
@@ -4574,25 +4571,25 @@
       </c>
       <c r="BA14" s="6"/>
       <c r="BB14" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="BC14" s="3" t="s">
         <v>89</v>
       </c>
       <c r="BD14" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="BE14" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="BF14" s="3" t="s">
         <v>128</v>
       </c>
       <c r="BG14" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="BH14" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="BH14" s="3" t="s">
-        <v>257</v>
       </c>
       <c r="BI14" s="3" t="s">
         <v>131</v>
@@ -4610,7 +4607,7 @@
         <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>65</v>
@@ -4622,7 +4619,7 @@
         <v>99</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I15" s="5">
         <v>7</v>
@@ -4658,22 +4655,22 @@
         <v>69</v>
       </c>
       <c r="T15" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="U15" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="U15" s="3" t="s">
+      <c r="V15" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="V15" s="3" t="s">
+      <c r="W15" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="W15" s="3" t="s">
+      <c r="X15" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="X15" s="3" t="s">
+      <c r="Y15" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>263</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>81</v>
@@ -4756,28 +4753,28 @@
       </c>
       <c r="BA15" s="6"/>
       <c r="BB15" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="BC15" s="3" t="s">
         <v>89</v>
       </c>
       <c r="BD15" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="BE15" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="BF15" s="3" t="s">
         <v>128</v>
       </c>
       <c r="BG15" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="BH15" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="BI15" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BJ15" s="6"/>
     </row>
@@ -4792,7 +4789,7 @@
         <v>115</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>65</v>
@@ -4846,7 +4843,7 @@
         <v>139</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="W16" s="3" t="s">
         <v>75</v>
@@ -4855,7 +4852,7 @@
         <v>138</v>
       </c>
       <c r="Y16" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Z16" s="3" t="s">
         <v>79</v>
@@ -4938,13 +4935,13 @@
       </c>
       <c r="BA16" s="6"/>
       <c r="BB16" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="BC16" s="3" t="s">
         <v>89</v>
       </c>
       <c r="BD16" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="BE16" s="3" t="s">
         <v>127</v>
@@ -4953,10 +4950,10 @@
         <v>128</v>
       </c>
       <c r="BG16" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="BH16" s="3" t="s">
         <v>269</v>
-      </c>
-      <c r="BH16" s="3" t="s">
-        <v>270</v>
       </c>
       <c r="BI16" s="3" t="s">
         <v>131</v>
@@ -4974,7 +4971,7 @@
         <v>115</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>65</v>
@@ -4983,10 +4980,10 @@
         <v>66</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I17" s="5">
         <v>6</v>
@@ -5022,22 +5019,22 @@
         <v>70</v>
       </c>
       <c r="T17" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="U17" s="3" t="s">
         <v>273</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>274</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>72</v>
       </c>
       <c r="W17" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="X17" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="X17" s="3" t="s">
+      <c r="Y17" s="3" t="s">
         <v>276</v>
-      </c>
-      <c r="Y17" s="3" t="s">
-        <v>277</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>79</v>
@@ -5120,7 +5117,7 @@
       </c>
       <c r="BA17" s="6"/>
       <c r="BB17" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="BC17" s="3" t="s">
         <v>89</v>
@@ -5129,19 +5126,19 @@
         <v>109</v>
       </c>
       <c r="BE17" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="BF17" s="3" t="s">
         <v>92</v>
       </c>
       <c r="BG17" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="BH17" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="BI17" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BJ17" s="6"/>
     </row>
@@ -5156,7 +5153,7 @@
         <v>115</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>65</v>
@@ -5168,7 +5165,7 @@
         <v>99</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I18" s="5">
         <v>5</v>
@@ -5204,22 +5201,22 @@
         <v>70</v>
       </c>
       <c r="T18" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="U18" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="U18" s="3" t="s">
+      <c r="V18" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="V18" s="3" t="s">
+      <c r="W18" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="W18" s="3" t="s">
+      <c r="X18" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="X18" s="3" t="s">
+      <c r="Y18" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="Y18" s="3" t="s">
-        <v>286</v>
       </c>
       <c r="Z18" s="3" t="s">
         <v>79</v>
@@ -5302,7 +5299,7 @@
       </c>
       <c r="BA18" s="6"/>
       <c r="BB18" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BC18" s="3" t="s">
         <v>89</v>
@@ -5317,16 +5314,16 @@
         <v>92</v>
       </c>
       <c r="BG18" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="BH18" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="BH18" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="BI18" s="3" t="s">
         <v>131</v>
       </c>
       <c r="BJ18" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
@@ -5340,19 +5337,19 @@
         <v>63</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>65</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>149</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I19" s="5">
         <v>2</v>
@@ -5364,22 +5361,22 @@
         <v>136</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P19" s="3" t="s">
         <v>136</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="R19" s="3" t="s">
         <v>136</v>
@@ -5388,22 +5385,22 @@
         <v>136</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="U19" s="3" t="s">
         <v>101</v>
       </c>
       <c r="V19" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="W19" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="W19" s="3" t="s">
+      <c r="X19" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="X19" s="3" t="s">
+      <c r="Y19" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="Y19" s="3" t="s">
-        <v>297</v>
       </c>
       <c r="Z19" s="3" t="s">
         <v>79</v>
@@ -5486,7 +5483,7 @@
       </c>
       <c r="BA19" s="6"/>
       <c r="BB19" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="BC19" s="3" t="s">
         <v>89</v>
@@ -5498,16 +5495,16 @@
         <v>127</v>
       </c>
       <c r="BF19" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="BG19" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="BH19" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BI19" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BJ19" s="6"/>
     </row>
@@ -5522,7 +5519,7 @@
         <v>63</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>65</v>
@@ -5570,13 +5567,13 @@
         <v>70</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>138</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>72</v>
@@ -5585,7 +5582,7 @@
         <v>139</v>
       </c>
       <c r="Y20" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>79</v>
@@ -5668,13 +5665,13 @@
       </c>
       <c r="BA20" s="6"/>
       <c r="BB20" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BC20" s="3" t="s">
         <v>89</v>
       </c>
       <c r="BD20" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="BE20" s="3" t="s">
         <v>110</v>
@@ -5683,13 +5680,13 @@
         <v>92</v>
       </c>
       <c r="BG20" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="BH20" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="BI20" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BJ20" s="6"/>
     </row>
